--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 84 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 82 clubs short</t>
         </is>
       </c>
     </row>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="P31" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="10" t="n">
         <v>2</v>
@@ -5630,7 +5630,7 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -9513,7 +9513,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -10580,7 +10580,7 @@
         <v>3</v>
       </c>
       <c r="Q102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -11991,7 +11991,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12061,8 +12061,8 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="9" t="n">
-        <v>0</v>
+      <c r="Z117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA117" s="10" t="n">
         <v>1</v>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -17216,7 +17216,7 @@
         <v>6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -17348,7 +17348,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 82 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 79 clubs short</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="S24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="9" t="n">
         <v>0</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T48" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V48" s="9" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -7987,8 +7987,8 @@
       <c r="Y75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z75" s="9" t="n">
-        <v>0</v>
+      <c r="Z75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA75" s="10" t="n">
         <v>1</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>1</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11700,7 +11700,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11770,8 +11770,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13583,8 +13583,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P133" s="9" t="n">
-        <v>3</v>
+      <c r="P133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q133" s="10" t="n">
         <v>2</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="S137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T137" s="10" t="n">
         <v>1</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14777,8 +14777,8 @@
       <c r="Y145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z145" s="9" t="n">
-        <v>0</v>
+      <c r="Z145" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA145" s="10" t="n">
         <v>1</v>
@@ -15145,7 +15145,7 @@
         <v>0</v>
       </c>
       <c r="S149" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T149" s="10" t="n">
         <v>1</v>
@@ -16754,7 +16754,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16919,7 +16919,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -17183,7 +17183,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -17315,13 +17315,13 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -17414,7 +17414,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 79 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 42 clubs short</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1197,8 +1197,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1391,8 +1391,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,8 +1779,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2070,8 +2070,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2943,8 +2943,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3234,8 +3234,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3428,8 +3428,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3525,8 +3525,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="10" t="n">
         <v>1</v>
@@ -4689,8 +4689,8 @@
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="9" t="n">
         <v>0</v>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5271,8 +5271,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5368,8 +5368,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5541,8 +5541,8 @@
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>1</v>
+      <c r="S50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5550,8 +5550,8 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>2</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5659,8 +5659,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
@@ -5756,8 +5756,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6115,10 +6115,10 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6435,8 +6435,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6514,8 +6514,8 @@
       <c r="S60" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T60" s="9" t="n">
-        <v>0</v>
+      <c r="T60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U60" s="9" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="9" t="n">
         <v>0</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8375,8 +8375,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8860,8 +8860,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="9" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -8939,8 +8939,8 @@
       <c r="S85" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T85" s="9" t="n">
-        <v>0</v>
+      <c r="T85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U85" s="9" t="n">
         <v>0</v>
@@ -9566,7 +9566,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9636,8 +9636,8 @@
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="9" t="n">
-        <v>0</v>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10148,7 +10148,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10218,8 +10218,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10245,7 +10245,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10315,8 +10315,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -10509,8 +10509,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10703,8 +10703,8 @@
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -10827,7 +10827,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -10897,8 +10897,8 @@
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
@@ -11118,7 +11118,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
@@ -11176,8 +11176,8 @@
       <c r="U108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="9" t="n">
-        <v>3</v>
+      <c r="V108" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11456,7 +11456,7 @@
         <v>2</v>
       </c>
       <c r="R111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S111" s="9" t="n">
         <v>0</v>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>0</v>
       </c>
       <c r="V120" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W120" s="9" t="n">
         <v>0</v>
@@ -12420,7 +12420,7 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="9" t="n">
         <v>0</v>
@@ -12670,7 +12670,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12740,8 +12740,8 @@
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" s="8" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -13419,8 +13419,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14901,7 +14901,7 @@
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15580,7 +15580,7 @@
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -15650,8 +15650,8 @@
       <c r="Y154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z154" s="9" t="n">
-        <v>0</v>
+      <c r="Z154" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA154" s="10" t="n">
         <v>1</v>
@@ -15727,7 +15727,7 @@
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T155" s="10" t="n">
         <v>1</v>
@@ -15844,8 +15844,8 @@
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA156" s="9" t="n">
         <v>0</v>
@@ -16259,7 +16259,7 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -16329,8 +16329,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -16457,7 +16457,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16523,7 +16523,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -16589,7 +16589,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16622,7 +16622,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -16721,7 +16721,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16754,7 +16754,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16787,7 +16787,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16820,7 +16820,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16952,7 +16952,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16985,7 +16985,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -17018,7 +17018,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -17051,7 +17051,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17084,7 +17084,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17117,7 +17117,7 @@
         <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17150,7 +17150,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17249,7 +17249,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17282,7 +17282,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -17414,7 +17414,7 @@
         <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -17480,7 +17480,7 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -17513,7 +17513,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 18 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 18 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 42 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 41 clubs short</t>
         </is>
       </c>
     </row>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L3" s="8" t="inlineStr">
         <is>
@@ -1044,17 +1044,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1238,17 +1238,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1335,13 +1335,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>1</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1573,11 +1573,11 @@
       <c r="U9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="9" t="n">
-        <v>0</v>
+      <c r="V9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W9" s="10" t="n">
+        <v>24</v>
       </c>
       <c r="X9" s="10" t="n">
         <v>4</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="9" t="n">
         <v>0</v>
@@ -2014,17 +2014,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2111,17 +2111,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2159,7 +2159,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>6</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L17" s="8" t="inlineStr">
         <is>
@@ -2402,17 +2402,17 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M18" s="7" t="n">
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2790,17 +2790,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2887,17 +2887,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -2984,17 +2984,17 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M24" s="7" t="n">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3119,8 +3119,8 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3178,13 +3178,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3372,17 +3372,17 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M28" s="7" t="n">
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W30" s="9" t="n">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>93</v>
+        <v>70</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>86</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3710,8 +3710,8 @@
       <c r="V31" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>3</v>
+      <c r="W31" s="10" t="n">
+        <v>8</v>
       </c>
       <c r="X31" s="10" t="n">
         <v>7</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -4098,8 +4098,8 @@
       <c r="V35" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>1</v>
+      <c r="W35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X35" s="10" t="n">
         <v>6</v>
@@ -4148,17 +4148,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -4245,17 +4245,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="7" t="n">
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4342,17 +4342,17 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M38" s="7" t="n">
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4439,13 +4439,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L41" s="8" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -4774,8 +4774,8 @@
       <c r="U42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V42" s="9" t="n">
-        <v>3</v>
+      <c r="V42" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>0</v>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="7" t="n">
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5118,17 +5118,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L48" s="8" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L49" s="8" t="inlineStr">
         <is>
@@ -5506,17 +5506,17 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M50" s="7" t="n">
@@ -5554,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>5</v>
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" s="8" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5950,8 +5950,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="8" t="inlineStr">
         <is>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L58" s="8" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6379,17 +6379,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
@@ -6423,8 +6423,8 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>2</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
@@ -6476,13 +6476,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X62" s="10" t="n">
         <v>4</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-36</v>
+        <v>-43</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -6908,11 +6908,11 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
+      <c r="V64" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W64" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="W64" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X64" s="10" t="n">
         <v>7</v>
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7006,7 +7006,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7349,17 +7349,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
@@ -7640,17 +7640,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="7" t="n">
@@ -7723,7 +7723,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -7775,8 +7775,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -7878,8 +7878,8 @@
       <c r="U74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="9" t="n">
-        <v>0</v>
+      <c r="V74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L76" s="8" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L78" s="8" t="inlineStr">
         <is>
@@ -8319,17 +8319,17 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L79" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M79" s="7" t="n">
@@ -8364,7 +8364,7 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8416,17 +8416,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L80" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M80" s="7" t="n">
@@ -8461,7 +8461,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="8" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
@@ -8849,7 +8849,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="8" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L86" s="8" t="inlineStr">
         <is>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9192,13 +9192,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9386,17 +9386,17 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L90" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M90" s="7" t="n">
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L93" s="8" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="8" t="inlineStr">
         <is>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L95" s="8" t="inlineStr">
         <is>
@@ -9968,13 +9968,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" s="8" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,13 +10065,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="8" t="inlineStr">
         <is>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" s="8" t="inlineStr">
         <is>
@@ -10259,13 +10259,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="8" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L100" s="8" t="inlineStr">
         <is>
@@ -10453,17 +10453,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,17 +10550,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -10579,8 +10579,8 @@
       <c r="P102" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>1</v>
+      <c r="Q102" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R102" s="9" t="n">
         <v>0</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="8" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="8" t="inlineStr">
         <is>
@@ -11326,13 +11326,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="8" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>0</v>
       </c>
       <c r="S110" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T110" s="10" t="n">
         <v>1</v>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11423,17 +11423,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L111" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="7" t="n">
@@ -11455,8 +11455,8 @@
       <c r="Q111" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R111" s="9" t="n">
-        <v>1</v>
+      <c r="R111" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S111" s="9" t="n">
         <v>0</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L112" s="8" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L113" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="7" t="n">
@@ -11661,8 +11661,8 @@
       <c r="U113" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11714,17 +11714,17 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L114" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M114" s="7" t="n">
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L115" s="8" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>4</v>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="L116" s="8" t="inlineStr">
         <is>
@@ -11952,8 +11952,8 @@
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="9" t="n">
-        <v>2</v>
+      <c r="V116" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="8" t="inlineStr">
         <is>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="8" t="inlineStr">
         <is>
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L119" s="8" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L120" s="8" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="8" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="8" t="inlineStr">
         <is>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="8" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="8" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L125" s="8" t="inlineStr">
         <is>
@@ -12825,8 +12825,8 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>3</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L126" s="8" t="inlineStr">
         <is>
@@ -12922,8 +12922,8 @@
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="9" t="n">
-        <v>1</v>
+      <c r="V126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L128" s="8" t="inlineStr">
         <is>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L129" s="8" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>0</v>
       </c>
       <c r="V129" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W129" s="9" t="n">
         <v>0</v>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="8" t="inlineStr">
         <is>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L131" s="8" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,17 +13460,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L132" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -13495,8 +13495,8 @@
       <c r="R132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="9" t="n">
-        <v>1</v>
+      <c r="S132" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T132" s="9" t="n">
         <v>0</v>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         </is>
       </c>
       <c r="P133" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q133" s="10" t="n">
         <v>2</v>
@@ -13593,7 +13593,7 @@
         <v>1</v>
       </c>
       <c r="S133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T133" s="10" t="n">
         <v>1</v>
@@ -13601,11 +13601,11 @@
       <c r="U133" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>5</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L134" s="8" t="inlineStr">
         <is>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L135" s="8" t="inlineStr">
         <is>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L138" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L138" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M138" s="7" t="n">
@@ -14086,8 +14086,8 @@
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>3</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="8" t="inlineStr">
         <is>
@@ -14236,17 +14236,17 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L140" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L140" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M140" s="7" t="n">
@@ -14263,7 +14263,7 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q140" s="10" t="n">
         <v>2</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L141" s="8" t="inlineStr">
         <is>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L142" s="8" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L144" s="8" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L146" s="8" t="inlineStr">
         <is>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L147" s="8" t="inlineStr">
         <is>
@@ -15012,17 +15012,17 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L148" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L148" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M148" s="7" t="n">
@@ -15057,7 +15057,7 @@
         <v>1</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15109,17 +15109,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L149" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="7" t="n">
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q150" s="9" t="n">
         <v>1</v>
@@ -15251,7 +15251,7 @@
         <v>2</v>
       </c>
       <c r="V150" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W150" s="9" t="n">
         <v>0</v>
@@ -15303,13 +15303,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L151" s="8" t="inlineStr">
         <is>
@@ -15400,13 +15400,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L152" s="8" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>0</v>
       </c>
       <c r="S152" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T152" s="9" t="n">
         <v>0</v>
@@ -15497,17 +15497,17 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L153" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M153" s="7" t="n">
@@ -15594,13 +15594,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L154" s="8" t="inlineStr">
         <is>
@@ -15691,13 +15691,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L155" s="8" t="inlineStr">
         <is>
@@ -15788,13 +15788,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L156" s="8" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>0</v>
       </c>
       <c r="V156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W156" s="9" t="n">
         <v>0</v>
@@ -15982,17 +15982,17 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L158" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L158" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M158" s="7" t="n">
@@ -16079,17 +16079,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L159" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="7" t="n">
@@ -16106,7 +16106,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -16124,7 +16124,7 @@
         <v>0</v>
       </c>
       <c r="V159" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16176,17 +16176,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L160" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="7" t="n">
@@ -16220,8 +16220,8 @@
       <c r="U160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="9" t="n">
-        <v>3</v>
+      <c r="V160" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
         <v>0</v>
@@ -16273,13 +16273,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L161" s="8" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -16490,7 +16490,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -16538,7 +16538,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -16571,7 +16571,7 @@
         <v>3</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -16589,7 +16589,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -16604,7 +16604,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -16637,7 +16637,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -16655,7 +16655,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -16703,7 +16703,7 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -16721,7 +16721,7 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -16736,7 +16736,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -16769,7 +16769,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -16787,7 +16787,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -16820,7 +16820,7 @@
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -16835,7 +16835,7 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -16853,7 +16853,7 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16868,7 +16868,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -16886,7 +16886,7 @@
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16901,7 +16901,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -16919,7 +16919,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16967,7 +16967,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -17033,7 +17033,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -17084,7 +17084,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17099,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -17150,7 +17150,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17165,7 +17165,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -17183,7 +17183,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -17198,7 +17198,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -17249,7 +17249,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -17315,7 +17315,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -17348,7 +17348,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -17363,7 +17363,7 @@
         <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -17429,7 +17429,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -17462,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -17495,7 +17495,7 @@
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -17513,7 +17513,7 @@
         <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -17528,7 +17528,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/213/inyear.xlsx
+++ b/docs/d/213/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>
